--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122747923</v>
+      </c>
+      <c r="B3" t="n">
+        <v>74761</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hocklet N, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>717619</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7173108</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122747922</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79770</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bräntkläppen SV, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>717659</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7172974</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>122747923</v>
       </c>
       <c r="B3" t="n">
-        <v>74761</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122747922</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>79872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747923</v>
+        <v>122747922</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,38 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717619</v>
+        <v>717659</v>
       </c>
       <c r="R3" t="n">
-        <v>7173108</v>
+        <v>7172974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747922</v>
+        <v>122747923</v>
       </c>
       <c r="B4" t="n">
-        <v>79872</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717659</v>
+        <v>717619</v>
       </c>
       <c r="R4" t="n">
-        <v>7172974</v>
+        <v>7173108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747922</v>
+        <v>122747923</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,38 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717659</v>
+        <v>717619</v>
       </c>
       <c r="R3" t="n">
-        <v>7172974</v>
+        <v>7173108</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747923</v>
+        <v>122747922</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717619</v>
+        <v>717659</v>
       </c>
       <c r="R4" t="n">
-        <v>7173108</v>
+        <v>7172974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747923</v>
+        <v>122747922</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,38 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717619</v>
+        <v>717659</v>
       </c>
       <c r="R3" t="n">
-        <v>7173108</v>
+        <v>7172974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747922</v>
+        <v>122747923</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717659</v>
+        <v>717619</v>
       </c>
       <c r="R4" t="n">
-        <v>7172974</v>
+        <v>7173108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>122747923</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122747922</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>79879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 50094-2024 artfynd.xlsx
+++ b/artfynd/A 50094-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>122747922</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>79881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
